--- a/测试集/边缘情况/重名列与无名列.xlsx
+++ b/测试集/边缘情况/重名列与无名列.xlsx
@@ -545,23 +545,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>朱婷</t>
+          <t>徐磊</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1883.33</v>
+        <v>1330.49</v>
       </c>
       <c r="D4" t="n">
-        <v>1777.33</v>
+        <v>1439.13</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>手工补录</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>330106199301019581</t>
+          <t>330106199101012744</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>杭州市西湖区文24号</t>
+          <t>杭州市西湖区文48号</t>
         </is>
       </c>
     </row>
@@ -573,14 +578,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周杰</t>
+          <t>朱婷</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1315.28</v>
+        <v>2488.73</v>
       </c>
       <c r="D5" t="n">
-        <v>198.75</v>
+        <v>1348.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -589,12 +594,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>330106198601018538</t>
+          <t>330106198801016315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>杭州市西湖区文38号</t>
+          <t>杭州市西湖区文73号</t>
         </is>
       </c>
     </row>
@@ -610,19 +615,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2241.53</v>
+        <v>1138.96</v>
       </c>
       <c r="D6" t="n">
-        <v>2620.46</v>
+        <v>2305.82</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>手工补录</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>330106199201018237</t>
+          <t>330106199301016746</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>杭州市西湖区文21号</t>
+          <t>杭州市西湖区文33号</t>
         </is>
       </c>
     </row>
@@ -634,14 +644,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>马超</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2462.83</v>
+        <v>1491.43</v>
       </c>
       <c r="D7" t="n">
-        <v>996</v>
+        <v>1144.49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -650,12 +660,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>330106197901012807</t>
+          <t>330106197101011379</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>杭州市西湖区文78号</t>
+          <t>杭州市西湖区文91号</t>
         </is>
       </c>
     </row>
@@ -667,28 +677,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>刘强</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105.61</v>
+        <v>1667.09</v>
       </c>
       <c r="D8" t="n">
-        <v>674.46</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>手工补录</t>
-        </is>
+        <v>1679.61</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>330106199201016213</t>
+          <t>330106197301016420</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>杭州市西湖区文94号</t>
+          <t>杭州市西湖区文56号</t>
         </is>
       </c>
     </row>
@@ -700,14 +705,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>徐磊</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>456.07</v>
+        <v>1213.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1075.67</v>
+        <v>2752.01</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -716,12 +721,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>330106198901018565</t>
+          <t>330106197001014379</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>杭州市西湖区文78号</t>
+          <t>杭州市西湖区文28号</t>
         </is>
       </c>
     </row>
